--- a/DateBase/orders/Nha Thu_2026-6-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-2.xlsx
@@ -518,7 +518,7 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,10 +520,93 @@
       <c r="C11" t="str">
         <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>259_诺拉_Nora_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>5</v>
+      </c>
+      <c r="C20" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>644_唐松草_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03111186258350</v>
+        <v>031111862583510530200020101059000</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-2.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>644_唐松草_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031111862583510530200020101059000</v>
+        <v>031111862583510530200020101059005</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-2.xlsx
@@ -598,6 +598,9 @@
       <c r="C20" t="str">
         <v>646_芍药莎拉_Sarah_undefined_5stems</v>
       </c>
+      <c r="F20" t="str">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="str">
@@ -664,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031111862583510530200020101059005</v>
+        <v>031111862583510530200020101059025</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-2.xlsx
@@ -599,7 +599,7 @@
         <v>646_芍药莎拉_Sarah_undefined_5stems</v>
       </c>
       <c r="F20" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -667,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031111862583510530200020101059025</v>
+        <v>0311118625835105302000201010590205</v>
       </c>
     </row>
   </sheetData>
